--- a/listing-research--amazon-keyword-map.xlsx
+++ b/listing-research--amazon-keyword-map.xlsx
@@ -1071,7 +1071,7 @@
     </x:row>
     <x:row r="37" ht="25" customHeight="1">
       <x:c r="A37" s="2" t="str">
-        <x:v>AI-assisted draft prepared for Joseph Berin. Review and explain the decisions before presenting this as your portfolio work.</x:v>
+        <x:v>Independent listing research. Review source facts and editorial decisions before publication.</x:v>
       </x:c>
       <x:c r="B37" s="2"/>
       <x:c r="C37" s="2"/>
